--- a/artfynd/A 12370-2022 artfynd.xlsx
+++ b/artfynd/A 12370-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12370-2022 artfynd.xlsx
+++ b/artfynd/A 12370-2022 artfynd.xlsx
@@ -2045,7 +2045,7 @@
         <v>112323388</v>
       </c>
       <c r="B15" t="n">
-        <v>5123</v>
+        <v>5166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 12370-2022 artfynd.xlsx
+++ b/artfynd/A 12370-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74387788</v>
+        <v>112322551</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jonsmyrsudden, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376706.1747655917</v>
+        <v>376720</v>
       </c>
       <c r="R2" t="n">
-        <v>6700846.761145526</v>
+        <v>6700740</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74387787</v>
+        <v>112323387</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jonsmyrsudden, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376743.0742182327</v>
+        <v>376577</v>
       </c>
       <c r="R3" t="n">
-        <v>6700709.108805587</v>
+        <v>6700274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74387789</v>
+        <v>112322556</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jonsmyrsudden, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376705.0533060161</v>
+        <v>376709</v>
       </c>
       <c r="R4" t="n">
-        <v>6700872.002629606</v>
+        <v>6700795</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74387785</v>
+        <v>112323385</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jonsmyrsudden, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376752.7952560482</v>
+        <v>376622</v>
       </c>
       <c r="R5" t="n">
-        <v>6700703.836269487</v>
+        <v>6700336</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,62 +1051,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112323372</v>
+        <v>112322581</v>
       </c>
       <c r="B6" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376710</v>
+        <v>376714</v>
       </c>
       <c r="R6" t="n">
-        <v>6700806</v>
+        <v>6700747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,49 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112322566</v>
+        <v>112322560</v>
       </c>
       <c r="B7" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376622</v>
+        <v>376713</v>
       </c>
       <c r="R7" t="n">
-        <v>6700395</v>
+        <v>6700739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1239,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1328,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112323374</v>
+        <v>112323375</v>
       </c>
       <c r="B8" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1344,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376704</v>
+        <v>376687</v>
       </c>
       <c r="R8" t="n">
-        <v>6700726</v>
+        <v>6700717</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112323367</v>
+        <v>112323376</v>
       </c>
       <c r="B9" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1470,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376725</v>
+        <v>376689</v>
       </c>
       <c r="R9" t="n">
-        <v>6700922</v>
+        <v>6700709</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112322618</v>
+        <v>112323383</v>
       </c>
       <c r="B10" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376594</v>
+        <v>376618</v>
       </c>
       <c r="R10" t="n">
-        <v>6700416</v>
+        <v>6700383</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,27 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112323371</v>
+        <v>112322566</v>
       </c>
       <c r="B11" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376715</v>
+        <v>376621</v>
       </c>
       <c r="R11" t="n">
-        <v>6700826</v>
+        <v>6700395</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,33 +1627,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112322556</v>
+        <v>112323382</v>
       </c>
       <c r="B12" t="n">
-        <v>73866</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,34 +1657,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376708</v>
+        <v>376621</v>
       </c>
       <c r="R12" t="n">
-        <v>6700795</v>
+        <v>6700398</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,27 +1731,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112322599</v>
+        <v>112323384</v>
       </c>
       <c r="B13" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,34 +1754,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>376732</v>
+        <v>376629</v>
       </c>
       <c r="R13" t="n">
-        <v>6700749</v>
+        <v>6700378</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,49 +1828,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112322573</v>
+        <v>112322589</v>
       </c>
       <c r="B14" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1980,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>376714</v>
+        <v>376532</v>
       </c>
       <c r="R14" t="n">
-        <v>6700904</v>
+        <v>6700274</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,55 +1937,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112323388</v>
+        <v>74387785</v>
       </c>
       <c r="B15" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Jonsmyrsudden, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>376539</v>
+        <v>376753</v>
       </c>
       <c r="R15" t="n">
-        <v>6700257</v>
+        <v>6700704</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,12 +2002,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2137,62 +2022,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112323376</v>
+        <v>74387786</v>
       </c>
       <c r="B16" t="n">
-        <v>81426</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Jonsmyrsudden, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>376690</v>
+        <v>376746</v>
       </c>
       <c r="R16" t="n">
-        <v>6700708</v>
+        <v>6700931</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,12 +2099,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2239,31 +2119,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112322631</v>
+        <v>74387787</v>
       </c>
       <c r="B17" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2287,14 +2162,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyrsudden, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>376695</v>
+        <v>376743</v>
       </c>
       <c r="R17" t="n">
-        <v>6700705</v>
+        <v>6700709</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,12 +2196,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2341,31 +2216,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112323368</v>
+        <v>74387788</v>
       </c>
       <c r="B18" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2389,14 +2259,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Jonsmyrsudden, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>376713</v>
+        <v>376706</v>
       </c>
       <c r="R18" t="n">
-        <v>6700923</v>
+        <v>6700847</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,12 +2293,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2443,62 +2313,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112323385</v>
+        <v>74387789</v>
       </c>
       <c r="B19" t="n">
-        <v>85891</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Jonsmyrsudden, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>376622</v>
+        <v>376705</v>
       </c>
       <c r="R19" t="n">
-        <v>6700336</v>
+        <v>6700872</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,12 +2390,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2545,62 +2410,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112323375</v>
+        <v>112322557</v>
       </c>
       <c r="B20" t="n">
-        <v>81426</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>376686</v>
+        <v>376675</v>
       </c>
       <c r="R20" t="n">
-        <v>6700716</v>
+        <v>6700598</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,31 +2507,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112323386</v>
+        <v>112322559</v>
       </c>
       <c r="B21" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2695,14 +2550,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>376616</v>
+        <v>376483</v>
       </c>
       <c r="R21" t="n">
-        <v>6700310</v>
+        <v>6700251</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,62 +2604,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112323387</v>
+        <v>112322564</v>
       </c>
       <c r="B22" t="n">
-        <v>77724</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>376577</v>
+        <v>376557</v>
       </c>
       <c r="R22" t="n">
-        <v>6700273</v>
+        <v>6700269</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,27 +2701,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112322581</v>
+        <v>112322567</v>
       </c>
       <c r="B23" t="n">
-        <v>77850</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2879,21 +2724,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2903,10 +2748,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>376714</v>
+        <v>376705</v>
       </c>
       <c r="R23" t="n">
-        <v>6700747</v>
+        <v>6700777</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2965,50 +2810,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112323384</v>
+        <v>112322573</v>
       </c>
       <c r="B24" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>376629</v>
+        <v>376714</v>
       </c>
       <c r="R24" t="n">
-        <v>6700378</v>
+        <v>6700904</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3055,62 +2895,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112323382</v>
+        <v>112322595</v>
       </c>
       <c r="B25" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>376622</v>
+        <v>376734</v>
       </c>
       <c r="R25" t="n">
-        <v>6700398</v>
+        <v>6700929</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,31 +2992,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112322559</v>
+        <v>112322598</v>
       </c>
       <c r="B26" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3209,10 +3039,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>376483</v>
+        <v>376602</v>
       </c>
       <c r="R26" t="n">
-        <v>6700251</v>
+        <v>6700269</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3271,19 +3101,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112323389</v>
+        <v>112322599</v>
       </c>
       <c r="B27" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3307,14 +3132,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>376538</v>
+        <v>376732</v>
       </c>
       <c r="R27" t="n">
-        <v>6700253</v>
+        <v>6700749</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3361,49 +3186,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112322560</v>
+        <v>112322618</v>
       </c>
       <c r="B28" t="n">
-        <v>81426</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3413,10 +3233,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>376713</v>
+        <v>376594</v>
       </c>
       <c r="R28" t="n">
-        <v>6700739</v>
+        <v>6700416</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3475,19 +3295,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112322564</v>
+        <v>112322622</v>
       </c>
       <c r="B29" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3515,10 +3330,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>376557</v>
+        <v>376710</v>
       </c>
       <c r="R29" t="n">
-        <v>6700269</v>
+        <v>6700741</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3577,50 +3392,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112323383</v>
+        <v>112322631</v>
       </c>
       <c r="B30" t="n">
-        <v>90847</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>376619</v>
+        <v>376696</v>
       </c>
       <c r="R30" t="n">
-        <v>6700383</v>
+        <v>6700705</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3667,31 +3477,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112323370</v>
+        <v>112323366</v>
       </c>
       <c r="B31" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3719,10 +3524,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>376719</v>
+        <v>376743</v>
       </c>
       <c r="R31" t="n">
-        <v>6700859</v>
+        <v>6700943</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3781,19 +3586,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112323373</v>
+        <v>112323367</v>
       </c>
       <c r="B32" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3821,10 +3621,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>376721</v>
+        <v>376725</v>
       </c>
       <c r="R32" t="n">
-        <v>6700785</v>
+        <v>6700922</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3883,50 +3683,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112322551</v>
+        <v>112323368</v>
       </c>
       <c r="B33" t="n">
-        <v>77724</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>376720</v>
+        <v>376713</v>
       </c>
       <c r="R33" t="n">
-        <v>6700740</v>
+        <v>6700923</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,62 +3768,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112322589</v>
+        <v>112323370</v>
       </c>
       <c r="B34" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>376532</v>
+        <v>376719</v>
       </c>
       <c r="R34" t="n">
-        <v>6700274</v>
+        <v>6700859</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4075,62 +3865,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112322623</v>
+        <v>112323371</v>
       </c>
       <c r="B35" t="n">
-        <v>73873</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>376691</v>
+        <v>376715</v>
       </c>
       <c r="R35" t="n">
-        <v>6700659</v>
+        <v>6700826</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4177,31 +3962,26 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112322598</v>
+        <v>112323372</v>
       </c>
       <c r="B36" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4225,14 +4005,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>376602</v>
+        <v>376710</v>
       </c>
       <c r="R36" t="n">
-        <v>6700269</v>
+        <v>6700806</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4279,31 +4059,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112322622</v>
+        <v>112323373</v>
       </c>
       <c r="B37" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4327,14 +4102,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>376710</v>
+        <v>376722</v>
       </c>
       <c r="R37" t="n">
-        <v>6700741</v>
+        <v>6700785</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4381,31 +4156,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112322567</v>
+        <v>112323374</v>
       </c>
       <c r="B38" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4429,14 +4199,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>376705</v>
+        <v>376703</v>
       </c>
       <c r="R38" t="n">
-        <v>6700777</v>
+        <v>6700726</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4483,15 +4253,602 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>112323377</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Jonsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>376673</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6700625</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>112323386</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Jonsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>376615</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6700310</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>112323389</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Jonsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>376538</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6700253</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>112322623</v>
+      </c>
+      <c r="B42" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gräsviggen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>376691</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6700659</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
           <t>Helena Malmestrand</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AX42" t="inlineStr">
         <is>
           <t>Helena Malmestrand</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>112322628</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gräsviggen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>376601</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6700448</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>112323388</v>
+      </c>
+      <c r="B44" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Jonsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>376539</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6700257</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12370-2022 artfynd.xlsx
+++ b/artfynd/A 12370-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322551</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323387</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322556</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323385</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322581</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322560</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323375</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323376</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323383</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322566</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323382</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323384</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322589</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387785</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387786</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2225,6 +2305,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387787</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2322,6 +2407,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387788</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2419,6 +2509,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387789</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2516,6 +2611,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322557</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2613,6 +2713,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322559</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2710,6 +2815,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322564</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2807,6 +2917,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322567</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2904,6 +3019,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322573</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3001,6 +3121,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322595</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3098,6 +3223,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322598</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3195,6 +3325,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322599</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3292,6 +3427,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322618</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3389,6 +3529,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322622</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3486,6 +3631,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322631</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3583,6 +3733,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323366</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3680,6 +3835,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323367</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3777,6 +3937,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323368</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3874,6 +4039,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323370</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3971,6 +4141,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323371</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4068,6 +4243,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323372</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4165,6 +4345,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323373</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4262,6 +4447,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323374</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4359,6 +4549,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323377</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4456,6 +4651,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323386</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4553,6 +4753,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323389</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4650,6 +4855,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322623</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4747,6 +4957,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322628</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4849,8 +5064,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323388</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>